--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MONTANA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MONTANA_2016.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C26">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C55">
